--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-10-2025.xlsx
@@ -544,22 +544,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>£11.17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£11.17</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>£10.35</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>£10.35</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£10.68</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -661,17 +661,17 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £11.80</t>
+                  £11.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.80</t>
+          <t>£13.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.80</t>
+          <t>£13.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£12.05</t>
+          <t>£11.68</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -788,22 +788,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>£15.95</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£15.95</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£15.50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>£15.10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>£15.10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£15.50</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£15.39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -910,22 +910,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>£16.95</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.95</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>£15.40</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£15.40</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£16.00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£15.67</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1032,22 +1032,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>£21.50</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>£19.60</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£19.60</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£20.25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£19.85</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1149,17 +1149,17 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.45</t>
+                  £21.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.45</t>
+          <t>£23.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.45</t>
+          <t>£23.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£21.79</t>
+          <t>£21.37</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£21.37</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.60</t>
+                  £21.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.60</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.60</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£22.54</t>
+          <t>£21.58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1393,17 +1393,17 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £24.86</t>
+                  £24.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£24.86</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£24.86</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£25.27</t>
+          <t>£24.77</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1515,17 +1515,17 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.95</t>
+                  £26.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£28.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£28.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£27.34</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1637,27 +1637,27 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.50</t>
+                  £26.20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>£28.95</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£28.95</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£27.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>£26.50</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£26.50</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£27.00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£27.39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1764,22 +1764,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>£37.95</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>£37.95</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>£35.13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>£35.13</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>£35.57</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1881,17 +1881,17 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.49</t>
+                  £32.35</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.49</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.49</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£34.10</t>
+          <t>£32.40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£39.76</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£39.76</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£40.27</t>
+          <t>£39.75</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£41.06</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2246,17 +2246,17 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.45</t>
+                  £39.99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>£44.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>£44.95</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£40.96</t>
+          <t>£39.50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£695.00</t>
+          <t>£729.95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£695.00</t>
+          <t>£729.95</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£895.00</t>
+          <t>£935.40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£895.00</t>
+          <t>£935.40</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£29.45</t>
+          <t>£32.75</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£29.45</t>
+          <t>£32.75</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£29.58</t>
+          <t>£29.52</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£35.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£39.10</t>
+          <t>£43.60</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£39.10</t>
+          <t>£43.60</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£40.21</t>
+          <t>£39.81</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£43.59</t>
+          <t>£48.65</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£43.59</t>
+          <t>£48.65</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£46.88</t>
+          <t>£44.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3076,32 +3076,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>£45.50</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>£49.60</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>£43.70</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>£43.70</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>£45.00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>£49.60</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>£43.99</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>£43.75</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£43.85</t>
+          <t>£43.80</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.85</t>
+          <t>£43.81</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>£925.00</t>
+          <t>£924.50</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£925.00</t>
+          <t>£924.50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£44.65</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£44.65</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff613391eb5+80197]
-	GetHandleVerifier [0x0x7ff613391f10+80288]
-	(No symbol) [0x0x7ff6131102fa]
-	(No symbol) [0x0x7ff613167cd7]
-	(No symbol) [0x0x7ff613167f9c]
-	(No symbol) [0x0x7ff6131bba87]
-	(No symbol) [0x0x7ff6131903bf]
-	(No symbol) [0x0x7ff6131b87fb]
-	(No symbol) [0x0x7ff613190153]
-	(No symbol) [0x0x7ff613158b02]
-	(No symbol) [0x0x7ff6131598d3]
-	GetHandleVerifier [0x0x7ff61364e83d+2949837]
-	GetHandleVerifier [0x0x7ff613648c6a+2926330]
-	GetHandleVerifier [0x0x7ff6136686c7+3055959]
-	GetHandleVerifier [0x0x7ff6133acfee+191102]
-	GetHandleVerifier [0x0x7ff6133b50af+224063]
-	GetHandleVerifier [0x0x7ff61339af64+117236]
-	GetHandleVerifier [0x0x7ff61339b119+117673]
-	GetHandleVerifier [0x0x7ff6133810a8+11064]
+	GetHandleVerifier [0x0x7ff73edd1eb5+80197]
+	GetHandleVerifier [0x0x7ff73edd1f10+80288]
+	(No symbol) [0x0x7ff73eb502fa]
+	(No symbol) [0x0x7ff73eba7cd7]
+	(No symbol) [0x0x7ff73eba7f9c]
+	(No symbol) [0x0x7ff73ebfba87]
+	(No symbol) [0x0x7ff73ebd03bf]
+	(No symbol) [0x0x7ff73ebf87fb]
+	(No symbol) [0x0x7ff73ebd0153]
+	(No symbol) [0x0x7ff73eb98b02]
+	(No symbol) [0x0x7ff73eb998d3]
+	GetHandleVerifier [0x0x7ff73f08e83d+2949837]
+	GetHandleVerifier [0x0x7ff73f088c6a+2926330]
+	GetHandleVerifier [0x0x7ff73f0a86c7+3055959]
+	GetHandleVerifier [0x0x7ff73edecfee+191102]
+	GetHandleVerifier [0x0x7ff73edf50af+224063]
+	GetHandleVerifier [0x0x7ff73eddaf64+117236]
+	GetHandleVerifier [0x0x7ff73eddb119+117673]
+	GetHandleVerifier [0x0x7ff73edc10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,150.00</t>
+          <t>£1,163.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,150.00</t>
+          <t>£1,163.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£1,268.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£1,268.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>£1,210.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>£1,210.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
